--- a/Bank_Soal_Matematika_PPTKA_Paket_B_FIX2.xlsx
+++ b/Bank_Soal_Matematika_PPTKA_Paket_B_FIX2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25ED2D51-FA4A-4D2A-8C5F-D5A5E0C87DAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{694C239C-3EA7-412E-A057-F51CAAE1DFDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
